--- a/storage/stats/euro/Eurojackpot_2026.xlsx
+++ b/storage/stats/euro/Eurojackpot_2026.xlsx
@@ -20,38 +20,95 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="50">
+  <si>
+    <t xml:space="preserve">28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
   <si>
     <t xml:space="preserve">10</t>
   </si>
   <si>
+    <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
     <t xml:space="preserve">37</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
     <t xml:space="preserve">47</t>
   </si>
   <si>
     <t xml:space="preserve">48</t>
   </si>
   <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
@@ -61,57 +118,21 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
     <t xml:space="preserve">34</t>
   </si>
   <si>
     <t xml:space="preserve">36</t>
   </si>
   <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
     <t xml:space="preserve">42</t>
   </si>
   <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41</t>
-  </si>
-  <si>
     <t xml:space="preserve">46</t>
   </si>
   <si>
     <t xml:space="preserve">24</t>
   </si>
   <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
     <t xml:space="preserve">44</t>
   </si>
   <si>
@@ -124,18 +145,9 @@
     <t xml:space="preserve">39</t>
   </si>
   <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
     <t xml:space="preserve">27</t>
   </si>
   <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
     <t xml:space="preserve">29</t>
   </si>
   <si>
@@ -145,15 +157,6 @@
     <t xml:space="preserve">14</t>
   </si>
   <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40</t>
-  </si>
-  <si>
     <t xml:space="preserve">38</t>
   </si>
   <si>
@@ -167,9 +170,6 @@
   </si>
   <si>
     <t xml:space="preserve">15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30</t>
   </si>
 </sst>
 </file>
@@ -381,7 +381,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -409,137 +409,137 @@
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="D5" s="1" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>16</v>
@@ -547,160 +547,160 @@
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>6</v>
@@ -708,71 +708,71 @@
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -780,19 +780,19 @@
         <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="F18" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>16</v>
@@ -800,68 +800,68 @@
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>16</v>
@@ -869,91 +869,91 @@
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D25" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>6</v>
@@ -961,22 +961,22 @@
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>5</v>
@@ -984,367 +984,367 @@
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>26</v>
-      </c>
       <c r="C29" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C35" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>7</v>
+        <v>49</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B41" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>6</v>
@@ -1352,114 +1352,114 @@
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>9</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>5</v>
@@ -1467,137 +1467,137 @@
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D48" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C53" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C53" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D53" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>16</v>
@@ -1605,117 +1605,278 @@
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C55" s="1" t="s">
+      <c r="D55" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F55" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D55" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="G55" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>49</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="B58" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C58" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D58" s="1" t="s">
+      <c r="F59" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E58" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="F58" s="1" t="s">
+      <c r="B60" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="F61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/storage/stats/euro/Eurojackpot_2026.xlsx
+++ b/storage/stats/euro/Eurojackpot_2026.xlsx
@@ -20,7 +20,52 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="50">
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24</t>
+  </si>
   <si>
     <t xml:space="preserve">28</t>
   </si>
@@ -28,9 +73,6 @@
     <t xml:space="preserve">26</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
     <t xml:space="preserve">30</t>
   </si>
   <si>
@@ -49,18 +91,12 @@
     <t xml:space="preserve">16</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
     <t xml:space="preserve">12</t>
   </si>
   <si>
     <t xml:space="preserve">9</t>
   </si>
   <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
     <t xml:space="preserve">1</t>
   </si>
   <si>
@@ -70,18 +106,12 @@
     <t xml:space="preserve">23</t>
   </si>
   <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
     <t xml:space="preserve">43</t>
   </si>
   <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
     <t xml:space="preserve">20</t>
   </si>
   <si>
@@ -91,24 +121,12 @@
     <t xml:space="preserve">41</t>
   </si>
   <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
     <t xml:space="preserve">37</t>
   </si>
   <si>
     <t xml:space="preserve">47</t>
   </si>
   <si>
-    <t xml:space="preserve">48</t>
-  </si>
-  <si>
     <t xml:space="preserve">21</t>
   </si>
   <si>
@@ -118,27 +136,12 @@
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
     <t xml:space="preserve">36</t>
   </si>
   <si>
-    <t xml:space="preserve">42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
     <t xml:space="preserve">44</t>
   </si>
   <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
     <t xml:space="preserve">19</t>
   </si>
   <si>
@@ -167,9 +170,6 @@
   </si>
   <si>
     <t xml:space="preserve">32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15</t>
   </si>
 </sst>
 </file>
@@ -381,7 +381,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -401,251 +401,251 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>35</v>
@@ -654,1229 +654,1298 @@
         <v>36</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>45</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="D31" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" s="1" t="s">
+      <c r="E36" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F36" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="G36" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B46" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C46" s="1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>17</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>31</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B50" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="E50" s="1" t="s">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="D52" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E52" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F52" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="G52" s="1" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B53" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="G53" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G53" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="G56" s="1" t="s">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>33</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="E61" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C61" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F61" s="1" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B65" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="F65" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F65" s="1" t="s">
+      <c r="F66" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="B68" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>11</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/storage/stats/euro/Eurojackpot_2026.xlsx
+++ b/storage/stats/euro/Eurojackpot_2026.xlsx
@@ -20,14 +20,32 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="50">
+  <si>
+    <t xml:space="preserve">45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
   <si>
     <t xml:space="preserve">7</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
     <t xml:space="preserve">50</t>
   </si>
   <si>
@@ -37,9 +55,6 @@
     <t xml:space="preserve">5</t>
   </si>
   <si>
-    <t xml:space="preserve">45</t>
-  </si>
-  <si>
     <t xml:space="preserve">25</t>
   </si>
   <si>
@@ -52,9 +67,6 @@
     <t xml:space="preserve">8</t>
   </si>
   <si>
-    <t xml:space="preserve">34</t>
-  </si>
-  <si>
     <t xml:space="preserve">15</t>
   </si>
   <si>
@@ -97,15 +109,9 @@
     <t xml:space="preserve">9</t>
   </si>
   <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
@@ -145,9 +151,6 @@
     <t xml:space="preserve">19</t>
   </si>
   <si>
-    <t xml:space="preserve">39</t>
-  </si>
-  <si>
     <t xml:space="preserve">27</t>
   </si>
   <si>
@@ -161,9 +164,6 @@
   </si>
   <si>
     <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49</t>
   </si>
   <si>
     <t xml:space="preserve">33</t>
@@ -381,7 +381,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G69"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -401,38 +401,38 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>11</v>
@@ -441,27 +441,27 @@
         <v>12</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>1</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>17</v>
@@ -470,79 +470,79 @@
         <v>18</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -550,22 +550,22 @@
         <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -573,226 +573,226 @@
         <v>32</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="D18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G18" s="1" t="s">
         <v>24</v>
@@ -803,272 +803,272 @@
         <v>2</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="E21" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>44</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C24" s="1" t="s">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>37</v>
+        <v>3</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D26" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="F26" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>23</v>
@@ -1076,876 +1076,899 @@
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>44</v>
+        <v>12</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="D35" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C39" s="1" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>23</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="B41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G41" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="C45" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1</v>
+        <v>23</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="D52" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E52" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="F52" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F54" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C54" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="G54" s="1" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="B57" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C57" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C57" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="D57" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>24</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="G67" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G67" s="1" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/storage/stats/euro/Eurojackpot_2026.xlsx
+++ b/storage/stats/euro/Eurojackpot_2026.xlsx
@@ -20,7 +20,40 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="50">
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7</t>
+  </si>
   <si>
     <t xml:space="preserve">45</t>
   </si>
@@ -40,27 +73,12 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50</t>
-  </si>
-  <si>
     <t xml:space="preserve">48</t>
   </si>
   <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
     <t xml:space="preserve">25</t>
   </si>
   <si>
-    <t xml:space="preserve">35</t>
-  </si>
-  <si>
     <t xml:space="preserve">46</t>
   </si>
   <si>
@@ -94,9 +112,6 @@
     <t xml:space="preserve">6</t>
   </si>
   <si>
-    <t xml:space="preserve">3</t>
-  </si>
-  <si>
     <t xml:space="preserve">11</t>
   </si>
   <si>
@@ -106,18 +121,12 @@
     <t xml:space="preserve">12</t>
   </si>
   <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
     <t xml:space="preserve">17</t>
   </si>
   <si>
-    <t xml:space="preserve">43</t>
-  </si>
-  <si>
     <t xml:space="preserve">20</t>
   </si>
   <si>
@@ -136,9 +145,6 @@
     <t xml:space="preserve">21</t>
   </si>
   <si>
-    <t xml:space="preserve">31</t>
-  </si>
-  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
@@ -160,13 +166,7 @@
     <t xml:space="preserve">18</t>
   </si>
   <si>
-    <t xml:space="preserve">14</t>
-  </si>
-  <si>
     <t xml:space="preserve">38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33</t>
   </si>
   <si>
     <t xml:space="preserve">32</t>
@@ -381,7 +381,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G69"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -412,183 +412,183 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G2" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -596,640 +596,640 @@
         <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E16" s="1" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D17" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F20" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="F28" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D35" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="G35" s="1" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>10</v>
@@ -1237,117 +1237,117 @@
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>2</v>
+        <v>44</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="B40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C40" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="D40" s="1" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>33</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="F42" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1355,295 +1355,295 @@
         <v>17</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E45" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>7</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D47" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F47" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G47" s="1" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="G49" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G50" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="D51" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G52" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>10</v>
@@ -1651,324 +1651,370 @@
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>7</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="D64" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F64" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G64" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C65" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="F65" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="C67" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D67" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="G67" s="1" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
